--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>101691805</v>
       </c>
       <c r="B2" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -735,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644956.6216150519</v>
+        <v>644957</v>
       </c>
       <c r="R2" t="n">
-        <v>6603086.435673047</v>
+        <v>6603086</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -795,12 +790,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johan  Tunberg </t>
+          <t>Johan  Tunberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johan  Tunberg </t>
+          <t>Johan  Tunberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
